--- a/AAII_Financials/Yearly/EZGO_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/EZGO_YR_FIN.xlsx
@@ -2574,7 +2574,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="E58" s="3">
         <v>7200</v>
@@ -2616,7 +2616,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="E59" s="3">
         <v>8100</v>
